--- a/pacjenci/MAREK RZEPKA.xlsx
+++ b/pacjenci/MAREK RZEPKA.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G2" t="n">

--- a/pacjenci/MAREK RZEPKA.xlsx
+++ b/pacjenci/MAREK RZEPKA.xlsx
@@ -413,279 +413,209 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>13.05.2021</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Ocena zaawansowania klinicznego.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  58min od podania 18F-FDG. Glikemia: 100mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Aktywne metabolicznie spakietowane i pojedyncze węzły chłonne grup:  -  I prawej wielkości wg PET 37x18mm, SUV max do 8,9, -  II prawej średnicy wg PET do 25mm, SUV max do 7,6,  -  III/V prawej wielkości wg PET do 47x30mm, SUV max do 11,3, -  IV prawej średnicy wg PET 30mm, SUV max do 7,8, -  III po lewej średnicy wg PET 15mm, SUV max 5,7, -  IV po lewej średnicy wg PET 20mm, SUV max 7,1, - podobojczykowe lewe średnicy wg PET do 15mm, SUV max do 7,3, - podobojczykowe prawe średnicy wg PET do 17mm, SUV max do 5,3. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Dyskretne przyścienne pogrubienie błony śluzowej obu zatok szczękowych.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie  węzły chłonne pachowe lewe średnicy wg PET do 12mm, SUV max do 4,2. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne przytchawicze prawe i  okna aortalno-płucnego średnicy do 13mm. Zwłóknienia w segmencie V płuca lewego.  Brzuch i miednica: Miernie aktywny metabolicznie obszar w topografii zwapnień w prostacie średnicy wg PET 12mm, SUV max 3,6. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapniony złóg w nerce lewej 4mm.  Pogrubienie lewego nadnercza w zakresie trzonu 14mm.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Obniżenie wysokości z włamaniem blaszek granicznych trzonu kręgu Th9.   Nasilone zmiany zwyrodnieniowe w odcinku szyjnym kregosłupa.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 1,9, Prawy płat wątroby SUVmax do 2,7.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie proces chłoniakowy z zajęciem węzłów chłonnych po obu stronach przepony.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>11.3</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>29.07.2021</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Ocena odpowiedzi po 2 cyklach chth.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  62min od podania 18F-FDG. Glikemia: 86mg%</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Miernie pobudzone metabolicznie węzeł chłonny grupy  III/V prawej wielkości wg PET 22x12mm SUV max 3,1. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Dyskretne przyścienne pogrubienie błony śluzowej lewej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Miernie pobudzone metabolicznie węzły chłonne pachowe lewe średnicy wg PET do 12mm, SUV max do 1,3. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne przytchawicze prawe i  okna aortalno-płucnego średnicy do 16mm. Zwłóknienia w segmencie 5 płuca lewego oraz w segm. 6/8 płuca prawego.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Pogrubienie lewego nadnercza w zakresie trzonu 14mm. Zwapnienia w powiększonej prostacie - do oceny urologicznej.  Układ kostny: Nieco niejednorodny metabolizm FDG w układzie kostnym. Obniżenie wysokości z włamaniem blaszek granicznych trzonu kręgu Th9.   Nasilone zmiany zwyrodnieniowe w odcinku szyjnym kregosłupa.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 1,3 Prawy płat wątroby SUVmax do 2,1.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono dobrą odpowiedź choroby chłoniakowej na stosowane leczenie.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>3.1</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>21.09.2021</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Ocena odpowiedzi po 4 cyklach chth.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 86mg%</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Miernie pobudzony mteabolicznie węzeł chłonny nadobojczykowy prawy wielkości 24mm, SUV max 2,5. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Dyskretne przyścienne pogrubienie błony śluzowej lewej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne w śródpiersiu, w dole pachowym prawym, przytchawicze prawe i  okna aortalno-płucnego  do 15x8mm. Zwłóknienia w segmencie 5 płuca lewego oraz w segm. 6/8 płuca prawego.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Pogrubienie lewego nadnercza w zakresie trzonu 14mm. Zwapnienia w powiększonej prostacie - do oceny urologicznej.  Układ kostny: Zwiększony metabolizm FDG w układzie kostnym - w pierwszej kolejności w związku ze stosowanym leczeniem. Obniżenie wysokości z włamaniem blaszek granicznych trzonu kręgu Th9.   Przebudowa tłuszczowa w jamach szpikowych kości ramiennych obustronnie.  Nasilone zmiany zwyrodnieniowe w odcinku szyjnym kregosłupa.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax do 2,4 Prawy płat wątroby SUVmax do 3,5.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech aktywnej metabolicznie choroby chłoniakowej . Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>3.5</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>30.08.2022</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Ocena remisji.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 115mg%</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Aktywne metabolicznie węzły chłonne: - 1B po stronie prawej średnicy wg PET do 10mm, SUV max do 4,7, - 2 po stronie prawej średnicy wg PET do 12mm, SUV max do 4,8, - 1A po stronie prawej średnicy wg PET 12mm, SUV max do 8,0, - 5A po stronie prawej  wielkości wg PET 21x39x43mm, SUV max do 10,9, - 3/4 po stronie prawej średnicy wg PET 28mm, SUV max do 7,8, - 4 po stronie lewej średnicy wg PET 13mm, SUV max do 6,4, - podobojczykowy lewy średnicy wg PET 10mm, SUV max 4,5,  - 5B po stronie prawej średnicy wg PET 20mm, SUV max 8,4. Symetryczna aktywność metaboliczna w topografii struktur pierścienia Waldeyera, SUV max do 5,4 - czynnościowa? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Dyskretne przyścienne pogrubienie błony śluzowej lewej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Pobudzony metabolicznie węzeł chłonny przytchawiczy dolny prawy średnicy wg PET 13mm, SUV max 3,2. Wnęka płuca lewego, SUV max 3,3. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne okna aortalno-płucnego  do 15x8mm. Zwłóknienia w segmencie 5 płuca lewego oraz w segm. 6/8 płuca prawego.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Pogrubienie lewego nadnercza w zakresie trzonu 14mm. Zwapnienia w powiększonej prostacie - do oceny urologicznej.  Układ kostny: Zwiększony metabolizm FDG w układzie kostnym - w pierwszej kolejności w związku ze stosowanym leczeniem. Obniżenie wysokości z włamaniem blaszek granicznych trzonu kręgu Th9.   Przebudowa tłuszczowa w jamach szpikowych kości ramiennych obustronnie. Nasilone zmiany zwyrodnieniowe w odcinku szyjnym kregosłupa.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax do 2,3, Prawy płat wątroby SUVmax do 3,6.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie węzłów chłonnych po jednej stronie przepony - w pierwszej kolejności wznowa choroby chłoniakowej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>10.9</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>01.06.2023</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Ocena aktualnego statusu choroby (nawrót chłoniaka Hodgkina 1 rok po zakończeniu leczenia). Porównano do poprzedniego badania PET/CT z dnia 30.08.2022r.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  59min od podania 18F-FDG. Glikemia: 101mg/dl</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Aktywne metabolicznie węzły chłonne (częściowo tworzące pakiety): - 2A po stronie prawej wlk. do 20x13mm, SUVmax 8,2 - 2B po stronie prawej wlk. 16x14mm, SUV max do 7,4, - 1A po stronie prawej średnicy 16mm, SUV max do 11,8, - 1A po stronie lewej średnicy 9mm, SUV max do 6,4, - 1B po stronie prawej średnicy do 16mm, SUV max do 7,2, - 1B po stronie lewej średnicy do 8mm, SUV max do 4,5, - 5 po stronie prawej  wielkości wg PET 33x40x53mm, SUV max do 11,5, -  3 i 4 po stronie prawej wielkości 31x27mm, SUV max do 10,5, - 3 i 4 po stronie lewej średnicy wg PET 13mm, SUV max do 6,4, - nadobojczykowe po stronie prawej: największy średnicy 24mm, SUVmax 8,3  [Im fuz 89], poza tym  średnicy 15mm, SUV max 11,0,  - podobojczykowy lewy średnicy 14mm, SUV max 7,7,   Symetryczna aktywność metaboliczna w topografii struktur pierścienia Waldeyera, SUV max do 5,2 - czynnościowa? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Dyskretne przyścienne pogrubienie błony śluzowej lewej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Pobudzony metabolicznie węzeł chłonny przytchawiczy dolny średnicy 13mm wg PET, SUV max 3,7. Pobudzone metabolicznie węzły chłonne okna aortalno-płucnego wlk. do 12x6mm, SUVmax 3,1. Wnęka płuca prawego SUV max 3,6 oraz lewego SUV max 3,1. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwłóknienia w segmencie 5 płuca lewego oraz w segm. 6/8 płuca prawego.  Brzuch i miednica: Aktywne metabolicznie węzły chłonne: - we wnęce wątroby oraz prawobocznie od ściany aorty brzusznej pomiędzy aortą i VCI, wielkości do 14x11mm, SUVmax do 6,9  [Im fuz 176], - lędźwiowe, poniżej naczyń nerkowych prawych, średnicy do 11mm, SUVmax 5,8  [Im fuz 180], - przedaortalny średnicy 6mm, SUVmax 4,2  [Im fuz 189]. Aktywne metabolicznie, drobne obszary w przyczepach mięśniowych do głowy kości udowych obustronnie oraz w mięśniu biodrowo-lędźwiowym prawym, SUVmax do 5,5 - w pierwszej kolejności czynnościowo. Pobudzenie metaboliczne w pętlach jelit - w pierwszej kolejności czynnościowo.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Pogrubienie lewego nadnercza w zakresie trzonu 14mm. Zwapnienia w powiększonej prostacie - do oceny urologicznej.  Układ kostny: Zwiększony metabolizm FDG w układzie kostnym - w pierwszej kolejności w związku ze stosowanym leczeniem. Obniżenie wysokości z włamaniem blaszek granicznych trzonu kręgu Th9.   Nasilone zmiany zwyrodnieniowe w odcinku szyjnym kregosłupa.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax do 1,9, Prawy płat wątroby SUVmax do 4,3.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie węzłów chłonnych po obu stronach przepony. Progresja choroby chłoniakowej w porównaniu do poprzedniego badania PET/CT z dnia 30.08.2022r. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>11.8</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>PD</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5 - znacznie zwiększony wychwyt lub nowe zmiany</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Progresja choroby. Klasyfikacja Lugano: Progressive Disease (PD) - progresja choroby. Deauville: 5 - znacznie zwiększony wychwyt lub nowe zmiany.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/MAREK RZEPKA.xlsx
+++ b/pacjenci/MAREK RZEPKA.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  58min od podania 18F-FDG. Glikemia: 100mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Aktywne metabolicznie spakietowane i pojedyncze węzły chłonne grup:  -  I prawej wielkości wg PET 37x18mm, SUV max do 8,9, -  II prawej średnicy wg PET do 25mm, SUV max do 7,6,  -  III/V prawej wielkości wg PET do 47x30mm, SUV max do 11,3, -  IV prawej średnicy wg PET 30mm, SUV max do 7,8, -  III po lewej średnicy wg PET 15mm, SUV max 5,7, -  IV po lewej średnicy wg PET 20mm, SUV max 7,1, - podobojczykowe lewe średnicy wg PET do 15mm, SUV max do 7,3, - podobojczykowe prawe średnicy wg PET do 17mm, SUV max do 5,3. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Dyskretne przyścienne pogrubienie błony śluzowej obu zatok szczękowych.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie  węzły chłonne pachowe lewe średnicy wg PET do 12mm, SUV max do 4,2. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne przytchawicze prawe i  okna aortalno-płucnego średnicy do 13mm. Zwłóknienia w segmencie V płuca lewego.  Brzuch i miednica: Miernie aktywny metabolicznie obszar w topografii zwapnień w prostacie średnicy wg PET 12mm, SUV max 3,6. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapniony złóg w nerce lewej 4mm.  Pogrubienie lewego nadnercza w zakresie trzonu 14mm.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Obniżenie wysokości z włamaniem blaszek granicznych trzonu kręgu Th9.   Nasilone zmiany zwyrodnieniowe w odcinku szyjnym kregosłupa.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 1,9, Prawy płat wątroby SUVmax do 2,7.</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie spakietowane i pojedyncze węzły chłonne grup:  -  I prawej wielkości wg PET 37x18mm, SUV max do 8,9, -  II prawej średnicy wg PET do 25mm, SUV max do 7,6,  -  III/V prawej wielkości wg PET do 47x30mm, SUV max do 11,3, -  IV prawej średnicy wg PET 30mm, SUV max do 7,8, -  III po lewej średnicy wg PET 15mm, SUV max 5,7, -  IV po lewej średnicy wg PET 20mm, SUV max 7,1, - podobojczykowe lewe średnicy wg PET do 15mm, SUV max do 7,3, - podobojczykowe prawe średnicy wg PET do 17mm, SUV max do 5,3. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Dyskretne przyścienne pogrubienie błony śluzowej obu zatok szczękowych.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie  węzły chłonne pachowe lewe średnicy wg PET do 12mm, SUV max do 4,2. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne przytchawicze prawe i  okna aortalno-płucnego średnicy do 13mm. Zwłóknienia w segmencie V płuca lewego.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Miernie aktywny metabolicznie obszar w topografii zwapnień w prostacie średnicy wg PET 12mm, SUV max 3,6. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapniony złóg w nerce lewej 4mm.  Pogrubienie lewego nadnercza w zakresie trzonu 14mm.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Obniżenie wysokości z włamaniem blaszek granicznych trzonu kręgu Th9.   Nasilone zmiany zwyrodnieniowe w odcinku szyjnym kregosłupa.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie proces chłoniakowy z zajęciem węzłów chłonnych po obu stronach przepony.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>11.3</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  62min od podania 18F-FDG. Glikemia: 86mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Miernie pobudzone metabolicznie węzeł chłonny grupy  III/V prawej wielkości wg PET 22x12mm SUV max 3,1. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Dyskretne przyścienne pogrubienie błony śluzowej lewej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Miernie pobudzone metabolicznie węzły chłonne pachowe lewe średnicy wg PET do 12mm, SUV max do 1,3. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne przytchawicze prawe i  okna aortalno-płucnego średnicy do 16mm. Zwłóknienia w segmencie 5 płuca lewego oraz w segm. 6/8 płuca prawego.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Pogrubienie lewego nadnercza w zakresie trzonu 14mm. Zwapnienia w powiększonej prostacie - do oceny urologicznej.  Układ kostny: Nieco niejednorodny metabolizm FDG w układzie kostnym. Obniżenie wysokości z włamaniem blaszek granicznych trzonu kręgu Th9.   Nasilone zmiany zwyrodnieniowe w odcinku szyjnym kregosłupa.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 1,3 Prawy płat wątroby SUVmax do 2,1.</t>
+          <t>86</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Miernie pobudzone metabolicznie węzeł chłonny grupy  III/V prawej wielkości wg PET 22x12mm SUV max 3,1. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Dyskretne przyścienne pogrubienie błony śluzowej lewej zatoki szczękowej.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Miernie pobudzone metabolicznie węzły chłonne pachowe lewe średnicy wg PET do 12mm, SUV max do 1,3. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne przytchawicze prawe i  okna aortalno-płucnego średnicy do 16mm. Zwłóknienia w segmencie 5 płuca lewego oraz w segm. 6/8 płuca prawego.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Pogrubienie lewego nadnercza w zakresie trzonu 14mm. Zwapnienia w powiększonej prostacie - do oceny urologicznej.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Nieco niejednorodny metabolizm FDG w układzie kostnym. Obniżenie wysokości z włamaniem blaszek granicznych trzonu kręgu Th9.   Nasilone zmiany zwyrodnieniowe w odcinku szyjnym kregosłupa.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono dobrą odpowiedź choroby chłoniakowej na stosowane leczenie.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>3.1</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 86mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Miernie pobudzony mteabolicznie węzeł chłonny nadobojczykowy prawy wielkości 24mm, SUV max 2,5. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Dyskretne przyścienne pogrubienie błony śluzowej lewej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne w śródpiersiu, w dole pachowym prawym, przytchawicze prawe i  okna aortalno-płucnego  do 15x8mm. Zwłóknienia w segmencie 5 płuca lewego oraz w segm. 6/8 płuca prawego.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Pogrubienie lewego nadnercza w zakresie trzonu 14mm. Zwapnienia w powiększonej prostacie - do oceny urologicznej.  Układ kostny: Zwiększony metabolizm FDG w układzie kostnym - w pierwszej kolejności w związku ze stosowanym leczeniem. Obniżenie wysokości z włamaniem blaszek granicznych trzonu kręgu Th9.   Przebudowa tłuszczowa w jamach szpikowych kości ramiennych obustronnie.  Nasilone zmiany zwyrodnieniowe w odcinku szyjnym kregosłupa.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax do 2,4 Prawy płat wątroby SUVmax do 3,5.</t>
+          <t>86</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Miernie pobudzony mteabolicznie węzeł chłonny nadobojczykowy prawy wielkości 24mm, SUV max 2,5. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Dyskretne przyścienne pogrubienie błony śluzowej lewej zatoki szczękowej.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne w śródpiersiu, w dole pachowym prawym, przytchawicze prawe i  okna aortalno-płucnego  do 15x8mm. Zwłóknienia w segmencie 5 płuca lewego oraz w segm. 6/8 płuca prawego.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Pogrubienie lewego nadnercza w zakresie trzonu 14mm. Zwapnienia w powiększonej prostacie - do oceny urologicznej.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Zwiększony metabolizm FDG w układzie kostnym - w pierwszej kolejności w związku ze stosowanym leczeniem. Obniżenie wysokości z włamaniem blaszek granicznych trzonu kręgu Th9.   Przebudowa tłuszczowa w jamach szpikowych kości ramiennych obustronnie.  Nasilone zmiany zwyrodnieniowe w odcinku szyjnym kregosłupa.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech aktywnej metabolicznie choroby chłoniakowej . Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>3.5</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 115mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Aktywne metabolicznie węzły chłonne: - 1B po stronie prawej średnicy wg PET do 10mm, SUV max do 4,7, - 2 po stronie prawej średnicy wg PET do 12mm, SUV max do 4,8, - 1A po stronie prawej średnicy wg PET 12mm, SUV max do 8,0, - 5A po stronie prawej  wielkości wg PET 21x39x43mm, SUV max do 10,9, - 3/4 po stronie prawej średnicy wg PET 28mm, SUV max do 7,8, - 4 po stronie lewej średnicy wg PET 13mm, SUV max do 6,4, - podobojczykowy lewy średnicy wg PET 10mm, SUV max 4,5,  - 5B po stronie prawej średnicy wg PET 20mm, SUV max 8,4. Symetryczna aktywność metaboliczna w topografii struktur pierścienia Waldeyera, SUV max do 5,4 - czynnościowa? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Dyskretne przyścienne pogrubienie błony śluzowej lewej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Pobudzony metabolicznie węzeł chłonny przytchawiczy dolny prawy średnicy wg PET 13mm, SUV max 3,2. Wnęka płuca lewego, SUV max 3,3. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne okna aortalno-płucnego  do 15x8mm. Zwłóknienia w segmencie 5 płuca lewego oraz w segm. 6/8 płuca prawego.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Pogrubienie lewego nadnercza w zakresie trzonu 14mm. Zwapnienia w powiększonej prostacie - do oceny urologicznej.  Układ kostny: Zwiększony metabolizm FDG w układzie kostnym - w pierwszej kolejności w związku ze stosowanym leczeniem. Obniżenie wysokości z włamaniem blaszek granicznych trzonu kręgu Th9.   Przebudowa tłuszczowa w jamach szpikowych kości ramiennych obustronnie. Nasilone zmiany zwyrodnieniowe w odcinku szyjnym kregosłupa.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax do 2,3, Prawy płat wątroby SUVmax do 3,6.</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne: - 1B po stronie prawej średnicy wg PET do 10mm, SUV max do 4,7, - 2 po stronie prawej średnicy wg PET do 12mm, SUV max do 4,8, - 1A po stronie prawej średnicy wg PET 12mm, SUV max do 8,0, - 5A po stronie prawej  wielkości wg PET 21x39x43mm, SUV max do 10,9, - 3/4 po stronie prawej średnicy wg PET 28mm, SUV max do 7,8, - 4 po stronie lewej średnicy wg PET 13mm, SUV max do 6,4, - podobojczykowy lewy średnicy wg PET 10mm, SUV max 4,5,  - 5B po stronie prawej średnicy wg PET 20mm, SUV max 8,4. Symetryczna aktywność metaboliczna w topografii struktur pierścienia Waldeyera, SUV max do 5,4 - czynnościowa? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Dyskretne przyścienne pogrubienie błony śluzowej lewej zatoki szczękowej.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Pobudzony metabolicznie węzeł chłonny przytchawiczy dolny prawy średnicy wg PET 13mm, SUV max 3,2. Wnęka płuca lewego, SUV max 3,3. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne okna aortalno-płucnego  do 15x8mm. Zwłóknienia w segmencie 5 płuca lewego oraz w segm. 6/8 płuca prawego.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Pogrubienie lewego nadnercza w zakresie trzonu 14mm. Zwapnienia w powiększonej prostacie - do oceny urologicznej.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Zwiększony metabolizm FDG w układzie kostnym - w pierwszej kolejności w związku ze stosowanym leczeniem. Obniżenie wysokości z włamaniem blaszek granicznych trzonu kręgu Th9.   Przebudowa tłuszczowa w jamach szpikowych kości ramiennych obustronnie. Nasilone zmiany zwyrodnieniowe w odcinku szyjnym kregosłupa.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie węzłów chłonnych po jednej stronie przepony - w pierwszej kolejności wznowa choroby chłoniakowej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>10.9</v>
       </c>
     </row>
@@ -601,20 +726,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  59min od podania 18F-FDG. Glikemia: 101mg/dl</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>: Aktywne metabolicznie węzły chłonne (częściowo tworzące pakiety): - 2A po stronie prawej wlk. do 20x13mm, SUVmax 8,2 - 2B po stronie prawej wlk. 16x14mm, SUV max do 7,4, - 1A po stronie prawej średnicy 16mm, SUV max do 11,8, - 1A po stronie lewej średnicy 9mm, SUV max do 6,4, - 1B po stronie prawej średnicy do 16mm, SUV max do 7,2, - 1B po stronie lewej średnicy do 8mm, SUV max do 4,5, - 5 po stronie prawej  wielkości wg PET 33x40x53mm, SUV max do 11,5, -  3 i 4 po stronie prawej wielkości 31x27mm, SUV max do 10,5, - 3 i 4 po stronie lewej średnicy wg PET 13mm, SUV max do 6,4, - nadobojczykowe po stronie prawej: największy średnicy 24mm, SUVmax 8,3  [Im fuz 89], poza tym  średnicy 15mm, SUV max 11,0,  - podobojczykowy lewy średnicy 14mm, SUV max 7,7,   Symetryczna aktywność metaboliczna w topografii struktur pierścienia Waldeyera, SUV max do 5,2 - czynnościowa? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Dyskretne przyścienne pogrubienie błony śluzowej lewej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Pobudzony metabolicznie węzeł chłonny przytchawiczy dolny średnicy 13mm wg PET, SUV max 3,7. Pobudzone metabolicznie węzły chłonne okna aortalno-płucnego wlk. do 12x6mm, SUVmax 3,1. Wnęka płuca prawego SUV max 3,6 oraz lewego SUV max 3,1. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwłóknienia w segmencie 5 płuca lewego oraz w segm. 6/8 płuca prawego.  Brzuch i miednica: Aktywne metabolicznie węzły chłonne: - we wnęce wątroby oraz prawobocznie od ściany aorty brzusznej pomiędzy aortą i VCI, wielkości do 14x11mm, SUVmax do 6,9  [Im fuz 176], - lędźwiowe, poniżej naczyń nerkowych prawych, średnicy do 11mm, SUVmax 5,8  [Im fuz 180], - przedaortalny średnicy 6mm, SUVmax 4,2  [Im fuz 189]. Aktywne metabolicznie, drobne obszary w przyczepach mięśniowych do głowy kości udowych obustronnie oraz w mięśniu biodrowo-lędźwiowym prawym, SUVmax do 5,5 - w pierwszej kolejności czynnościowo. Pobudzenie metaboliczne w pętlach jelit - w pierwszej kolejności czynnościowo.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Pogrubienie lewego nadnercza w zakresie trzonu 14mm. Zwapnienia w powiększonej prostacie - do oceny urologicznej.  Układ kostny: Zwiększony metabolizm FDG w układzie kostnym - w pierwszej kolejności w związku ze stosowanym leczeniem. Obniżenie wysokości z włamaniem blaszek granicznych trzonu kręgu Th9.   Nasilone zmiany zwyrodnieniowe w odcinku szyjnym kregosłupa.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax do 1,9, Prawy płat wątroby SUVmax do 4,3.</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne (częściowo tworzące pakiety): - 2A po stronie prawej wlk. do 20x13mm, SUVmax 8,2 - 2B po stronie prawej wlk. 16x14mm, SUV max do 7,4, - 1A po stronie prawej średnicy 16mm, SUV max do 11,8, - 1A po stronie lewej średnicy 9mm, SUV max do 6,4, - 1B po stronie prawej średnicy do 16mm, SUV max do 7,2, - 1B po stronie lewej średnicy do 8mm, SUV max do 4,5, - 5 po stronie prawej  wielkości wg PET 33x40x53mm, SUV max do 11,5, -  3 i 4 po stronie prawej wielkości 31x27mm, SUV max do 10,5, - 3 i 4 po stronie lewej średnicy wg PET 13mm, SUV max do 6,4, - nadobojczykowe po stronie prawej: największy średnicy 24mm, SUVmax 8,3  [Im fuz 89], poza tym  średnicy 15mm, SUV max 11,0,  - podobojczykowy lewy średnicy 14mm, SUV max 7,7,   Symetryczna aktywność metaboliczna w topografii struktur pierścienia Waldeyera, SUV max do 5,2 - czynnościowa? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Dyskretne przyścienne pogrubienie błony śluzowej lewej zatoki szczękowej.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Pobudzony metabolicznie węzeł chłonny przytchawiczy dolny średnicy 13mm wg PET, SUV max 3,7. Pobudzone metabolicznie węzły chłonne okna aortalno-płucnego wlk. do 12x6mm, SUVmax 3,1. Wnęka płuca prawego SUV max 3,6 oraz lewego SUV max 3,1. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwłóknienia w segmencie 5 płuca lewego oraz w segm. 6/8 płuca prawego.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne: - we wnęce wątroby oraz prawobocznie od ściany aorty brzusznej pomiędzy aortą i VCI, wielkości do 14x11mm, SUVmax do 6,9  [Im fuz 176], - lędźwiowe, poniżej naczyń nerkowych prawych, średnicy do 11mm, SUVmax 5,8  [Im fuz 180], - przedaortalny średnicy 6mm, SUVmax 4,2  [Im fuz 189]. Aktywne metabolicznie, drobne obszary w przyczepach mięśniowych do głowy kości udowych obustronnie oraz w mięśniu biodrowo-lędźwiowym prawym, SUVmax do 5,5 - w pierwszej kolejności czynnościowo. Pobudzenie metaboliczne w pętlach jelit - w pierwszej kolejności czynnościowo.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Pogrubienie lewego nadnercza w zakresie trzonu 14mm. Zwapnienia w powiększonej prostacie - do oceny urologicznej.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Zwiększony metabolizm FDG w układzie kostnym - w pierwszej kolejności w związku ze stosowanym leczeniem. Obniżenie wysokości z włamaniem blaszek granicznych trzonu kręgu Th9.   Nasilone zmiany zwyrodnieniowe w odcinku szyjnym kregosłupa.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie węzłów chłonnych po obu stronach przepony. Progresja choroby chłoniakowej w porównaniu do poprzedniego badania PET/CT z dnia 30.08.2022r. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="L6" t="n">
         <v>11.8</v>
       </c>
     </row>
